--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_41.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2520995.057303665</v>
+        <v>2514128.064355009</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162900723</v>
+        <v>286.4107162898233</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162900723</v>
+        <v>286.4107162898233</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -793,10 +793,10 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>385</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>129.4037835029435</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -857,7 +857,7 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>325.839266425598</v>
+        <v>324.2480957795422</v>
       </c>
       <c r="R4" t="n">
         <v>326.6021279811511</v>
@@ -897,7 +897,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>39.04534712526427</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -948,7 +948,7 @@
         <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>277.9274879340253</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -979,16 +979,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>102.4466513351298</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1027,10 +1027,10 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>385</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>385</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>10.33915573984979</v>
+        <v>39.04534712526427</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1213,19 +1213,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>199.8180013219744</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>66.5639999646113</v>
+        <v>223.7250803601599</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
@@ -1270,7 +1270,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1328,7 +1328,7 @@
         <v>240.445564079015</v>
       </c>
       <c r="P10" t="n">
-        <v>287.4478973282775</v>
+        <v>285.8567266822253</v>
       </c>
       <c r="Q10" t="n">
         <v>325.839266425598</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>236.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>299.2212965486107</v>
+        <v>303.1866879340253</v>
       </c>
       <c r="V11" t="n">
         <v>279.8510241668239</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>97.23431917176904</v>
       </c>
       <c r="C12" t="n">
         <v>11.09991244551929</v>
@@ -1495,7 +1495,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T12" t="n">
         <v>55.35776521751382</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1620,10 +1620,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>86.93822665041519</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
         <v>55.35776521751382</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1966,10 +1966,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>547.2737972923793</v>
+        <v>267.2794625959092</v>
       </c>
       <c r="S18" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T18" t="n">
         <v>55.35776521751382</v>
@@ -2170,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>118.0355277429562</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U21" t="n">
         <v>50.21035976018675</v>
@@ -2325,7 +2325,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G23" t="n">
         <v>53.75737228701621</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2401,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T24" t="n">
         <v>55.35776521751382</v>
@@ -2632,7 +2632,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>84.14143263308497</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2677,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U27" t="n">
         <v>50.21035976018675</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>144.8481678023229</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2932,10 +2932,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X30" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -3042,10 +3042,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I32" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>34.55655664632661</v>
+        <v>115.0662319853481</v>
       </c>
       <c r="C33" t="n">
         <v>11.09991244551929</v>
@@ -3112,16 +3112,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>262.0138729201192</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3400,7 +3400,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
@@ -3409,7 +3409,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>97.23431917176916</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
@@ -3823,13 +3823,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="43">
@@ -3984,7 +3984,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G44" t="n">
         <v>53.75737228701621</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>239.5984974349628</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4114,7 +4114,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>69.86273944538755</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
@@ -4330,16 +4330,16 @@
         <v>30.8</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="N2" t="n">
-        <v>411.95</v>
+        <v>396.55</v>
       </c>
       <c r="O2" t="n">
-        <v>793.0999999999999</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="C3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="D3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>585.6429020987573</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H3" t="n">
         <v>250.1195817084329</v>
@@ -4421,31 +4421,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S3" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>964.8227613033797</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>964.6102766971304</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>949.9530371097363</v>
+        <v>400.8938473128077</v>
       </c>
       <c r="W3" t="n">
-        <v>917.2528927563742</v>
+        <v>270.182954885592</v>
       </c>
       <c r="X3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.189519579215</v>
+        <v>250.1195817084329</v>
       </c>
     </row>
     <row r="4">
@@ -4455,49 +4455,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253.9666383453244</v>
+        <v>256.125934252978</v>
       </c>
       <c r="C4" t="n">
-        <v>379.9686441637601</v>
+        <v>256.125934252978</v>
       </c>
       <c r="D4" t="n">
-        <v>493.2877882887602</v>
+        <v>282.3059186249661</v>
       </c>
       <c r="E4" t="n">
-        <v>611.1166925001733</v>
+        <v>400.1348228363792</v>
       </c>
       <c r="F4" t="n">
-        <v>735.4776650921087</v>
+        <v>524.4957954283146</v>
       </c>
       <c r="G4" t="n">
-        <v>888.884230978994</v>
+        <v>677.9023613151999</v>
       </c>
       <c r="H4" t="n">
-        <v>1058.400816138392</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="I4" t="n">
-        <v>1279.533695074475</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J4" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
         <v>360.7011393749001</v>
@@ -4506,25 +4506,25 @@
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="X4" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="Y4" t="n">
-        <v>142.2093006790323</v>
+        <v>256.125934252978</v>
       </c>
     </row>
     <row r="5">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
         <v>52.03227202568092</v>
@@ -4564,19 +4564,19 @@
         <v>411.95</v>
       </c>
       <c r="L5" t="n">
-        <v>777.6999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="N5" t="n">
         <v>1158.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4591,19 +4591,19 @@
         <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.2814659950806</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>134.2814659950806</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>134.2814659950806</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E6" t="n">
-        <v>134.2814659950806</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="F6" t="n">
-        <v>134.2814659950806</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G6" t="n">
-        <v>134.2814659950806</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4670,19 +4670,19 @@
         <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>575.9338724144908</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>187.0449835256019</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>154.3448391722397</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X6" t="n">
-        <v>134.2814659950806</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>134.2814659950806</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>404.0685093339813</v>
+        <v>1247.586867406406</v>
       </c>
       <c r="C7" t="n">
-        <v>530.0705151524171</v>
+        <v>1373.588873224842</v>
       </c>
       <c r="D7" t="n">
-        <v>643.3896592774172</v>
+        <v>1486.908017349842</v>
       </c>
       <c r="E7" t="n">
-        <v>761.2185634888302</v>
+        <v>1540</v>
       </c>
       <c r="F7" t="n">
-        <v>885.5795360807657</v>
+        <v>1540</v>
       </c>
       <c r="G7" t="n">
-        <v>1038.986101967651</v>
+        <v>1540</v>
       </c>
       <c r="H7" t="n">
-        <v>1208.502687127049</v>
+        <v>1540</v>
       </c>
       <c r="I7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M7" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N7" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O7" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P7" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>30.8</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>30.8</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X7" t="n">
-        <v>180.9018709886569</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y7" t="n">
-        <v>292.3111716676892</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="8">
@@ -4777,19 +4777,19 @@
         <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E8" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G8" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
@@ -4810,10 +4810,10 @@
         <v>1158.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="P8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>897.189519579215</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="C9" t="n">
-        <v>897.189519579215</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="E9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="F9" t="n">
-        <v>695.3531546075237</v>
+        <v>30.8</v>
       </c>
       <c r="G9" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4901,25 +4901,25 @@
         <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>970.2346453614745</v>
+        <v>811.4860793053647</v>
       </c>
       <c r="T9" t="n">
-        <v>964.8227613033797</v>
+        <v>806.0741952472699</v>
       </c>
       <c r="U9" t="n">
-        <v>964.6102766971304</v>
+        <v>805.8617106410206</v>
       </c>
       <c r="V9" t="n">
-        <v>949.9530371097363</v>
+        <v>791.2044710536265</v>
       </c>
       <c r="W9" t="n">
-        <v>917.2528927563742</v>
+        <v>402.3155821647376</v>
       </c>
       <c r="X9" t="n">
-        <v>897.189519579215</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="Y9" t="n">
-        <v>897.189519579215</v>
+        <v>382.2522089875785</v>
       </c>
     </row>
     <row r="10">
@@ -4929,46 +4929,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>848.8849663319327</v>
+        <v>813.2558574435027</v>
       </c>
       <c r="C10" t="n">
-        <v>974.8869721503685</v>
+        <v>939.2578632619385</v>
       </c>
       <c r="D10" t="n">
-        <v>974.8869721503685</v>
+        <v>939.2578632619385</v>
       </c>
       <c r="E10" t="n">
-        <v>1092.715876361782</v>
+        <v>1057.086767473352</v>
       </c>
       <c r="F10" t="n">
-        <v>1217.076848953717</v>
+        <v>1149.350535904523</v>
       </c>
       <c r="G10" t="n">
-        <v>1370.483414840602</v>
+        <v>1149.350535904523</v>
       </c>
       <c r="H10" t="n">
-        <v>1540</v>
+        <v>1318.86712106392</v>
       </c>
       <c r="I10" t="n">
-        <v>1540</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="J10" t="n">
-        <v>1540</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="K10" t="n">
-        <v>1540</v>
+        <v>1540.000000000003</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012348</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.36440448452</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038373</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878529</v>
       </c>
       <c r="P10" t="n">
         <v>689.8317115219688</v>
@@ -4980,25 +4980,25 @@
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>218.8756791588049</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>465.4268717970915</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>664.2482646830374</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W10" t="n">
-        <v>664.2482646830374</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="X10" t="n">
-        <v>737.4756656529004</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="Y10" t="n">
-        <v>848.8849663319327</v>
+        <v>701.4985197772105</v>
       </c>
     </row>
     <row r="11">
@@ -5038,19 +5038,19 @@
         <v>598.13</v>
       </c>
       <c r="L11" t="n">
-        <v>733.1420762183976</v>
+        <v>598.13</v>
       </c>
       <c r="M11" t="n">
-        <v>1243.990904947333</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N11" t="n">
-        <v>1243.990904947333</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O11" t="n">
-        <v>1797.400904947332</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="P11" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5059,10 +5059,10 @@
         <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U11" t="n">
         <v>1544.373295489988</v>
@@ -5138,25 +5138,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T12" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W12" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X12" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y12" t="n">
-        <v>444.3729990826727</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="13">
@@ -5166,16 +5166,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C13" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D13" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E13" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F13" t="n">
         <v>1153.55685638681</v>
@@ -5220,22 +5220,22 @@
         <v>44.72</v>
       </c>
       <c r="T13" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X13" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="14">
@@ -5263,28 +5263,28 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L14" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M14" t="n">
-        <v>1108.978828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N14" t="n">
-        <v>1662.388828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O14" t="n">
-        <v>2215.798828728935</v>
+        <v>2236</v>
       </c>
       <c r="P14" t="n">
         <v>2236</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G15" t="n">
-        <v>44.72</v>
+        <v>132.5363905559749</v>
       </c>
       <c r="H15" t="n">
         <v>44.72</v>
@@ -5372,28 +5372,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S15" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U15" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V15" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W15" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X15" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y15" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="16">
@@ -5509,22 +5509,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>1129.18</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N17" t="n">
-        <v>1682.59</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.93203277325181</v>
+        <v>402.0654643105373</v>
       </c>
       <c r="C18" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="D18" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E18" t="n">
         <v>44.72</v>
@@ -5609,28 +5609,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>647.3506049216877</v>
+        <v>930.1731652211525</v>
       </c>
       <c r="S18" t="n">
-        <v>466.2983195781991</v>
+        <v>812.4317511154845</v>
       </c>
       <c r="T18" t="n">
-        <v>410.3813850150538</v>
+        <v>756.5148165523393</v>
       </c>
       <c r="U18" t="n">
-        <v>359.6638499037541</v>
+        <v>705.7972814410396</v>
       </c>
       <c r="V18" t="n">
-        <v>294.5015598113094</v>
+        <v>640.6349913485949</v>
       </c>
       <c r="W18" t="n">
-        <v>211.2963649528968</v>
+        <v>557.4297964901822</v>
       </c>
       <c r="X18" t="n">
-        <v>140.7279412706871</v>
+        <v>486.8613728079725</v>
       </c>
       <c r="Y18" t="n">
-        <v>90.8376455473191</v>
+        <v>436.9710770846045</v>
       </c>
     </row>
     <row r="19">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F19" t="n">
         <v>1153.55685638681</v>
@@ -5694,22 +5694,22 @@
         <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="20">
@@ -5743,25 +5743,25 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1151.54</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>1151.54</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N20" t="n">
-        <v>1704.95</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F21" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G21" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H21" t="n">
         <v>44.72</v>
@@ -5849,25 +5849,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F23" t="n">
         <v>157.615990899539</v>
@@ -5980,52 +5980,52 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L23" t="n">
-        <v>1243.990904947333</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M23" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="N23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="O23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
         <v>44.72</v>
@@ -6083,28 +6083,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D25" t="n">
         <v>1010.366979583462</v>
@@ -6174,16 +6174,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="26">
@@ -6217,22 +6217,22 @@
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K26" t="n">
-        <v>989.4391130376558</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="L26" t="n">
-        <v>1171.741171271065</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M26" t="n">
+        <v>575.7700000000003</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1129.18</v>
+      </c>
+      <c r="O26" t="n">
         <v>1682.59</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2236</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2236</v>
       </c>
       <c r="P26" t="n">
         <v>2236</v>
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C27" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
         <v>44.72</v>
@@ -6320,28 +6320,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S27" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6457,7 +6457,7 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L29" t="n">
         <v>733.1420762183976</v>
@@ -6478,28 +6478,28 @@
         <v>2236</v>
       </c>
       <c r="R29" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S29" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C30" t="n">
         <v>44.72</v>
@@ -6575,10 +6575,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6685,31 +6685,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>179.7320762183977</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L32" t="n">
-        <v>179.7320762183977</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M32" t="n">
-        <v>690.5809049473327</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N32" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>472.7782575464261</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C33" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D33" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E33" t="n">
-        <v>387.7869114524009</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H33" t="n">
         <v>44.72</v>
@@ -6928,25 +6928,25 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>179.7320762183977</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>179.7320762183977</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M35" t="n">
-        <v>690.5809049473327</v>
+        <v>1682.59</v>
       </c>
       <c r="N35" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>935.4919426714454</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>817.7505285657774</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>761.8335940026321</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>711.1160588913324</v>
       </c>
       <c r="V36" t="n">
-        <v>357.8124310491301</v>
+        <v>645.9537687988877</v>
       </c>
       <c r="W36" t="n">
-        <v>274.6072361907175</v>
+        <v>562.7485739404751</v>
       </c>
       <c r="X36" t="n">
-        <v>204.0388125085078</v>
+        <v>492.1801502582655</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="37">
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
@@ -7168,16 +7168,16 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L38" t="n">
-        <v>436.0291130376557</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M38" t="n">
-        <v>946.8779417665908</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N38" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O38" t="n">
         <v>1797.400904947332</v>
@@ -7189,28 +7189,28 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>409.4673863086053</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="40">
@@ -7299,22 +7299,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
         <v>1377.480007433093</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7405,22 +7405,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665908</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="O41" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E42" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="F42" t="n">
-        <v>373.7498342171993</v>
+        <v>44.72</v>
       </c>
       <c r="G42" t="n">
         <v>44.72</v>
@@ -7526,7 +7526,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>507.6838703204934</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="43">
@@ -7627,13 +7627,13 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7642,22 +7642,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>946.8779417665908</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N44" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="O44" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>297.950717050992</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
         <v>44.72</v>
@@ -7739,31 +7739,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>826.0584179616072</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S45" t="n">
-        <v>708.3170038559392</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T45" t="n">
-        <v>652.400069292794</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U45" t="n">
-        <v>601.6825341814942</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V45" t="n">
-        <v>536.5202440890496</v>
+        <v>648.036913346663</v>
       </c>
       <c r="W45" t="n">
-        <v>453.3150492306369</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>382.7466255484273</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>332.8563298250593</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7827,7 +7827,7 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
         <v>372.6360891248843</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>929.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O2" t="n">
         <v>455.2478695740924</v>
@@ -7985,7 +7985,7 @@
         <v>385.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>542.2671287719298</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8207,22 +8207,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>369.4444444444444</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8453,13 +8453,13 @@
         <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8681,22 +8681,22 @@
         <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>20.69228354680773</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
@@ -8927,10 +8927,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>629.2478695740924</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P14" t="n">
-        <v>20.69228354680773</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
         <v>172.8226843274854</v>
@@ -9152,7 +9152,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9164,13 +9164,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>606.6620109882336</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,16 +9623,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
         <v>1036.248958069835</v>
@@ -9644,7 +9644,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="L26" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,10 +9875,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q26" t="n">
         <v>172.8226843274854</v>
@@ -10100,10 +10100,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>300.1141042229715</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>171.4188408091284</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,13 +10586,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,19 +10811,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O41" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,25 +11285,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22715,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.59117064605573</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23186,7 +23186,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.591170646052205</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -26311,7 +26311,7 @@
         <v>1290861.46634091</v>
       </c>
       <c r="P2" t="n">
-        <v>1290861.466340909</v>
+        <v>1290861.46634091</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656947</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511878</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>527352.5986435077</v>
+        <v>525836.7429551921</v>
       </c>
       <c r="C6" t="n">
-        <v>664930.5787773223</v>
+        <v>663414.7230890061</v>
       </c>
       <c r="D6" t="n">
-        <v>666991.3506896381</v>
+        <v>665475.4950013227</v>
       </c>
       <c r="E6" t="n">
-        <v>343108.063114375</v>
+        <v>341366.2133012674</v>
       </c>
       <c r="F6" t="n">
-        <v>686298.9584598789</v>
+        <v>684557.1086467713</v>
       </c>
       <c r="G6" t="n">
-        <v>688244.5349280648</v>
+        <v>686502.6851149569</v>
       </c>
       <c r="H6" t="n">
-        <v>690192.811745366</v>
+        <v>688450.9619322583</v>
       </c>
       <c r="I6" t="n">
-        <v>692143.8083887262</v>
+        <v>690401.9585756186</v>
       </c>
       <c r="J6" t="n">
-        <v>278577.5445903511</v>
+        <v>276835.6947772437</v>
       </c>
       <c r="K6" t="n">
-        <v>696054.0403425705</v>
+        <v>694312.190529463</v>
       </c>
       <c r="L6" t="n">
-        <v>698013.3159028298</v>
+        <v>696271.4660897219</v>
       </c>
       <c r="M6" t="n">
-        <v>638727.3917988098</v>
+        <v>636985.541985702</v>
       </c>
       <c r="N6" t="n">
-        <v>701940.288833663</v>
+        <v>700198.4390205548</v>
       </c>
       <c r="O6" t="n">
-        <v>423908.0280914011</v>
+        <v>422166.1782782931</v>
       </c>
       <c r="P6" t="n">
-        <v>705878.6309424106</v>
+        <v>704136.7811293033</v>
       </c>
     </row>
   </sheetData>
@@ -26984,31 +26984,31 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>-0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>350</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>-0</v>
       </c>
-      <c r="J2" t="n">
-        <v>350</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>-0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
@@ -27039,31 +27039,31 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -27115,7 +27115,7 @@
         <v>-0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3083845693742</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27572,10 +27572,10 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>29.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>302.969359406885</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>311.9806467141294</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>298.3662265384588</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,7 +27676,7 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="E5" t="n">
         <v>400</v>
@@ -27727,7 +27727,7 @@
         <v>400</v>
       </c>
       <c r="U5" t="n">
-        <v>371.2938086145854</v>
+        <v>400</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27758,16 +27758,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>142.8540958999382</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>229.7214358512913</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27806,10 +27806,10 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>15.21035976018675</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>29.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27837,25 +27837,25 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>334.6091701401468</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>399.0616969338014</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27913,7 +27913,7 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="E8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27992,19 +27992,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>139.8182410159025</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28037,7 +28037,7 @@
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>242.8389196044513</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28049,7 +28049,7 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28077,16 +28077,16 @@
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>367.5785816557937</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
@@ -28131,10 +28131,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>321.4107171168378</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28195,13 +28195,13 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T11" t="n">
         <v>350</v>
       </c>
       <c r="U11" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="V11" t="n">
         <v>350</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="C12" t="n">
         <v>350</v>
@@ -28274,7 +28274,7 @@
         <v>350</v>
       </c>
       <c r="S12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>350</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -28314,7 +28314,7 @@
         <v>350</v>
       </c>
       <c r="F13" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G13" t="n">
         <v>350</v>
@@ -28356,7 +28356,7 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
@@ -28399,10 +28399,10 @@
         <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28475,10 +28475,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
@@ -28508,10 +28508,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S15" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T15" t="n">
         <v>350</v>
@@ -28706,7 +28706,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28745,10 +28745,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>279.9943346964701</v>
       </c>
       <c r="S18" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T18" t="n">
         <v>350</v>
@@ -28788,7 +28788,7 @@
         <v>350</v>
       </c>
       <c r="F19" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G19" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28949,10 +28949,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
@@ -28985,10 +28985,10 @@
         <v>350</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T21" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="U21" t="n">
         <v>350</v>
@@ -29104,7 +29104,7 @@
         <v>350</v>
       </c>
       <c r="F23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G23" t="n">
         <v>350</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29180,10 +29180,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
@@ -29219,10 +29219,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T24" t="n">
         <v>350</v>
@@ -29256,7 +29256,7 @@
         <v>350</v>
       </c>
       <c r="D25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E25" t="n">
         <v>350</v>
@@ -29310,7 +29310,7 @@
         <v>350</v>
       </c>
       <c r="V25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W25" t="n">
         <v>350</v>
@@ -29411,7 +29411,7 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29420,7 +29420,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
         <v>325.7395358750273</v>
@@ -29456,13 +29456,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
       </c>
       <c r="T27" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="U27" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S29" t="n">
         <v>350</v>
@@ -29645,10 +29645,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -29711,10 +29711,10 @@
         <v>350</v>
       </c>
       <c r="X30" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31">
@@ -29821,10 +29821,10 @@
         <v>350</v>
       </c>
       <c r="H32" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I32" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="C33" t="n">
         <v>350</v>
@@ -29891,16 +29891,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>217.1263858913485</v>
@@ -30125,7 +30125,7 @@
         <v>350</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30167,7 +30167,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>285.25992437226</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30179,7 +30179,7 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
@@ -30188,7 +30188,7 @@
         <v>350</v>
       </c>
       <c r="Y36" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37">
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30368,7 +30368,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124345</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30453,7 +30453,7 @@
         <v>350</v>
       </c>
       <c r="H40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="I40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
@@ -30602,13 +30602,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>255.7338705714974</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="43">
@@ -30763,7 +30763,7 @@
         <v>350</v>
       </c>
       <c r="F44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G44" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30842,7 +30842,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>100.0377449029141</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
@@ -30875,10 +30875,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30893,7 +30893,7 @@
         <v>350</v>
       </c>
       <c r="W45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>350</v>
@@ -30963,10 +30963,10 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="V46" t="n">
         <v>350</v>
@@ -34752,10 +34752,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="O2" t="n">
         <v>385</v>
@@ -34764,7 +34764,7 @@
         <v>385</v>
       </c>
       <c r="Q2" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>26.44442865857389</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34901,10 +34901,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>263.097277702551</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34986,22 +34986,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>369.4444444444444</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N5" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>385</v>
-      </c>
-      <c r="O5" t="n">
-        <v>385</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35123,25 +35123,25 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>53.62826530319025</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>151.6180515036939</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35232,13 +35232,13 @@
         <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35363,16 +35363,16 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>93.19572568805175</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
         <v>189.9754334937423</v>
@@ -35417,10 +35417,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>73.96707168673028</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35460,22 +35460,22 @@
         <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O11" t="n">
         <v>559</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35600,7 +35600,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F13" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G13" t="n">
         <v>104.95612715847</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
@@ -35691,7 +35691,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
@@ -35706,10 +35706,10 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P14" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35931,7 +35931,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -35943,13 +35943,13 @@
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36074,7 +36074,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F19" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G19" t="n">
         <v>104.95612715847</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>536.4141414141411</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,16 +36402,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
         <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
         <v>559</v>
@@ -36423,7 +36423,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36542,7 +36542,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D25" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E25" t="n">
         <v>69.01909516304346</v>
@@ -36596,7 +36596,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W25" t="n">
         <v>123.6271901612903</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="L26" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,10 +36654,10 @@
         <v>559</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>300.1141042229715</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37128,13 +37128,13 @@
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,13 +37350,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
@@ -37365,13 +37365,13 @@
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37590,19 +37590,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H40" t="n">
-        <v>121.2288738983814</v>
+        <v>113.4402045325156</v>
       </c>
       <c r="I40" t="n">
         <v>173.3665443798817</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38064,25 +38064,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38249,10 +38249,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V46" t="n">
         <v>150.8296897837838</v>
